--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 17:15 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 21:56 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:13 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:21 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38200,7 +38200,7 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38294,7 +38294,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>(100091) - All Ritmo Cancún Resort &amp; Waterpark</t>
+          <t>All Ritmo Cancún Resort &amp; Waterpark</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -38304,7 +38304,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -38339,7 +38339,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>(100699) - Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
+          <t>Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -38349,7 +38349,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -38384,7 +38384,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>(104094) - Hotel Almirante Cartagena</t>
+          <t>Hotel Almirante Cartagena</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -38394,7 +38394,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>(556527) - Masquerade Tower at Rio Hotel</t>
+          <t>Masquerade Tower at Rio Hotel</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -38439,7 +38439,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -38474,7 +38474,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>(450703) - Holiday Inn Express Melbourne Little Collins by IHG</t>
+          <t>Holiday Inn Express Melbourne Little Collins by IHG</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -38484,7 +38484,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -38519,7 +38519,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>(404605) - Hyatt Place Marlborough/Apex Center</t>
+          <t>Hyatt Place Marlborough/Apex Center</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -38529,7 +38529,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -38564,7 +38564,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>(100455) - Paradise Village Beach Resort</t>
+          <t>Paradise Village Beach Resort</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -38574,7 +38574,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -38609,7 +38609,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>(153885) - Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -38619,7 +38619,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -38654,7 +38654,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>(104173) - Sol Caribe Sea Flower</t>
+          <t>Sol Caribe Sea Flower</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -38664,7 +38664,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -38699,7 +38699,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>(481765) - Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
+          <t>Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -38709,7 +38709,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>(324901) - Paris Las Vegas Resort &amp; Casino</t>
+          <t>Paris Las Vegas Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -38754,7 +38754,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -38789,7 +38789,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>(160813) - Holiday Inn Express Portland West/Hillsboro by IHG</t>
+          <t>Holiday Inn Express Portland West/Hillsboro by IHG</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -38799,7 +38799,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -38834,7 +38834,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>(130860) - ANA InterContinental Manza Beach Resort by IHG</t>
+          <t>ANA InterContinental Manza Beach Resort by IHG</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -38844,7 +38844,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -38879,7 +38879,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>(124195) - Holiday Inn Express Hotel &amp; Suites Meadowlands Area by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Meadowlands Area by IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -38889,7 +38889,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -38924,7 +38924,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>(102834) - Holiday Inn Santo Domingo</t>
+          <t>Holiday Inn Santo Domingo</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -38934,7 +38934,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -38969,7 +38969,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>(103579) - Caribe Royale Orlando</t>
+          <t>Caribe Royale Orlando</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -39014,7 +39014,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>(100384) - Meliá Puerto Vallarta All Inclusive</t>
+          <t>Meliá Puerto Vallarta All Inclusive</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -39024,7 +39024,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -39059,7 +39059,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>(113476) - Holiday Inn Express London - Croydon by IHG</t>
+          <t>Holiday Inn Express London - Croydon by IHG</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -39069,7 +39069,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -39104,7 +39104,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>(252206) - Hyatt Centric The Loop Chicago</t>
+          <t>Hyatt Centric The Loop Chicago</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -39114,7 +39114,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -39149,7 +39149,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>(547672) - Hotel Indigo TOKYO SHIBUYA by IHG</t>
+          <t>Hotel Indigo TOKYO SHIBUYA by IHG</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -39159,7 +39159,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -39194,7 +39194,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>(155801) - Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -39204,7 +39204,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -39239,7 +39239,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>(188728) - ANA InterContinental Ishigaki Resort by IHG</t>
+          <t>ANA InterContinental Ishigaki Resort by IHG</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -39249,7 +39249,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>(111210) - Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
+          <t>Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -39294,7 +39294,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -39329,7 +39329,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>(135880) - Crowne Plaza Limassol by IHG</t>
+          <t>Crowne Plaza Limassol by IHG</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -39339,7 +39339,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>(306731) - Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -39384,7 +39384,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -39419,7 +39419,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>(162083) - Tropicana Laughlin</t>
+          <t>Tropicana Laughlin</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -39429,7 +39429,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -39464,7 +39464,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>(109744) - Holiday Inn NYC - Lower East Side by IHG</t>
+          <t>Holiday Inn NYC - Lower East Side by IHG</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -39474,7 +39474,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -39509,7 +39509,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>(319646) - Grand Hyatt Bogota</t>
+          <t>Grand Hyatt Bogota</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -39519,7 +39519,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -39554,7 +39554,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>(120946) - voco Dubai by IHG</t>
+          <t>voco Dubai by IHG</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -39564,7 +39564,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -39599,7 +39599,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>(102609) - Golden Nugget Las Vegas Hotel &amp; Casino</t>
+          <t>Golden Nugget Las Vegas Hotel &amp; Casino</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -39609,7 +39609,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>HotelBeds</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -39644,7 +39644,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>(479128) - La Mer Resort &amp; Spa Crete</t>
+          <t>La Mer Resort &amp; Spa Crete</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>(167825) - Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -39699,7 +39699,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -39734,7 +39734,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>(227892) - Holiday Inn Express London Wandsworth by IHG</t>
+          <t>Holiday Inn Express London Wandsworth by IHG</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -39744,7 +39744,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -39779,7 +39779,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>(154983) - Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -39789,7 +39789,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -39824,7 +39824,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>(211802) - Voco Gold Coast</t>
+          <t>Voco Gold Coast</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -39834,7 +39834,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -39869,7 +39869,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>(104963) - Sofitel New York</t>
+          <t>Sofitel New York</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -39879,7 +39879,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -39914,7 +39914,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>(111976) - Holiday Inn Munich - South by IHG</t>
+          <t>Holiday Inn Munich - South by IHG</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>(307905) - Holiday Inn Express &amp; Suites Lancaster East - Strasburg by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Lancaster East - Strasburg by IHG</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -39969,7 +39969,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>(309593) - Holiday Inn Express &amp; Suites Orlando at SeaWorld by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Orlando at SeaWorld by IHG</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -40014,7 +40014,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -40049,7 +40049,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>(129761) - InterContinental Osaka by IHG</t>
+          <t>InterContinental Osaka by IHG</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -40059,7 +40059,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -40094,7 +40094,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>(100371) - Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
+          <t>Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -40104,7 +40104,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -40139,7 +40139,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>(158151) - Holiday Inn Kansas City Downtown by IHG</t>
+          <t>Holiday Inn Kansas City Downtown by IHG</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -40149,7 +40149,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -40184,7 +40184,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>(322551) - Ocean El Faro</t>
+          <t>Ocean El Faro</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -40194,7 +40194,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -40229,7 +40229,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>(267834) - Holiday Inn Express - Edinburgh City Centre by IHG</t>
+          <t>Holiday Inn Express - Edinburgh City Centre by IHG</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -40239,7 +40239,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -40274,7 +40274,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>(128412) - InterContinental Sydney by IHG</t>
+          <t>InterContinental Sydney by IHG</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -40284,7 +40284,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -40319,7 +40319,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>(100468) - Playa Suites Acapulco</t>
+          <t>Playa Suites Acapulco</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -40329,7 +40329,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -40364,7 +40364,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>(481271) - Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
+          <t>Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -40374,7 +40374,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -40409,7 +40409,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>(114442) - Crowne Plaza Budapest by IHG</t>
+          <t>Crowne Plaza Budapest by IHG</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -40419,7 +40419,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -40454,7 +40454,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>(211749) - Crowne Plaza Surfers Paradise by IHG</t>
+          <t>Crowne Plaza Surfers Paradise by IHG</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -40464,7 +40464,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -40499,7 +40499,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>(113331) - Holiday Inn London-Bloomsbury Hotel by IHG</t>
+          <t>Holiday Inn London-Bloomsbury Hotel by IHG</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -40509,7 +40509,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -40544,7 +40544,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>(107811) - Hyatt Regency Washington on Capitol Hill</t>
+          <t>Hyatt Regency Washington on Capitol Hill</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -40554,7 +40554,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -40589,7 +40589,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>(425153) - Hotel Indigo London - 1 Leicester Square by IHG</t>
+          <t>Hotel Indigo London - 1 Leicester Square by IHG</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -40599,7 +40599,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -40634,7 +40634,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>(116629) - Embassy Suites by Hilton Philadelphia Airport</t>
+          <t>Embassy Suites by Hilton Philadelphia Airport</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -40644,7 +40644,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -40679,7 +40679,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>(107736) - Embassy Suites by Hilton Orlando Airport</t>
+          <t>Embassy Suites by Hilton Orlando Airport</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -40689,7 +40689,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -40724,7 +40724,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>(111030) - Holiday Inn Express New York - Manhattan West Side by IHG</t>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -40769,7 +40769,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>(512307) - Holiday Inn Orlando International Dr-ICON by IHG</t>
+          <t>Holiday Inn Orlando International Dr-ICON by IHG</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -40779,7 +40779,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -40814,7 +40814,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>(219851) - Holiday Inn Bristol City Centre by IHG</t>
+          <t>Holiday Inn Bristol City Centre by IHG</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -40824,7 +40824,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -40859,7 +40859,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>(228567) - Kimpton Charlotte Square by IHG</t>
+          <t>Kimpton Charlotte Square by IHG</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -40904,7 +40904,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>(129903) - RIHGA Royal Hotel Osaka, Vignette Collection by IHG</t>
+          <t>RIHGA Royal Hotel Osaka, Vignette Collection by IHG</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -40914,7 +40914,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -40949,7 +40949,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>(100328) - Imperial Las Perlas</t>
+          <t>Imperial Las Perlas</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -40959,7 +40959,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -40994,7 +40994,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>(210653) - Royalton Riviera Cancun, An Autograph Collection All-Inclusive Resort &amp; Casino</t>
+          <t>Royalton Riviera Cancun, An Autograph Collection All-Inclusive Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -41004,7 +41004,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -41039,7 +41039,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>(129766) - Holiday Inn Osaka Namba by IHG</t>
+          <t>Holiday Inn Osaka Namba by IHG</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -41049,7 +41049,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -41084,7 +41084,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>(506020) - Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -41094,7 +41094,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -41129,7 +41129,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>(136246) - Holiday Inn Tbilisi by IHG</t>
+          <t>Holiday Inn Tbilisi by IHG</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>(165366) - Crowne Plaza College Park - Washington DC by IHG</t>
+          <t>Crowne Plaza College Park - Washington DC by IHG</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -41184,7 +41184,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -41219,7 +41219,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>(546925) - Crowne Plaza PHU QUOC STARBAY by IHG</t>
+          <t>Crowne Plaza PHU QUOC STARBAY by IHG</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -41229,7 +41229,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -41264,7 +41264,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>(481409) - Holiday Inn Express MUNICH - CITY EAST by IHG</t>
+          <t>Holiday Inn Express MUNICH - CITY EAST by IHG</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -41274,7 +41274,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -41309,7 +41309,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>(123825) - Hotel Indigo Glasgow by IHG</t>
+          <t>Hotel Indigo Glasgow by IHG</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -41354,7 +41354,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>(493382) - Holiday Inn &amp; Suites Jakarta Gajah Mada by IHG</t>
+          <t>Holiday Inn &amp; Suites Jakarta Gajah Mada by IHG</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -41364,7 +41364,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -41399,7 +41399,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>(283467) - Holiday Inn Express London - ExCeL by IHG</t>
+          <t>Holiday Inn Express London - ExCeL by IHG</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -41409,7 +41409,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -41444,7 +41444,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>(105159) - Crowne Plaza Newark Airport by IHG</t>
+          <t>Crowne Plaza Newark Airport by IHG</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -41454,7 +41454,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -41489,7 +41489,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>(211757) - Crowne Plaza Melbourne by IHG</t>
+          <t>Crowne Plaza Melbourne by IHG</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -41499,7 +41499,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -41534,7 +41534,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>(111965) - Crowne Plaza Frankfurt Congress Hotel by IHG</t>
+          <t>Crowne Plaza Frankfurt Congress Hotel by IHG</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -41544,7 +41544,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -41579,7 +41579,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>(121035) - InterContinental Marseille - Hotel Dieu by IHG</t>
+          <t>InterContinental Marseille - Hotel Dieu by IHG</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -41624,7 +41624,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>(492790) - Holiday Inn Express Liverpool Central by IHG</t>
+          <t>Holiday Inn Express Liverpool Central by IHG</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -41634,7 +41634,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -41669,7 +41669,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>(239652) - Holiday Inn Express &amp; Suites Miami Airport East by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Miami Airport East by IHG</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -41679,7 +41679,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -41714,7 +41714,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>(228651) - InterContinental Edinburgh The George by IHG</t>
+          <t>InterContinental Edinburgh The George by IHG</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -41759,7 +41759,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>(117463) - Grand Hyatt Denver</t>
+          <t>Grand Hyatt Denver</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -41769,7 +41769,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -41804,7 +41804,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>(107757) - Kimpton Theta New York - Times Square by IHG</t>
+          <t>Kimpton Theta New York - Times Square by IHG</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -41814,7 +41814,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -41849,7 +41849,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>(167152) - Holiday Inn Express &amp; Suites Asheville Downtown by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Asheville Downtown by IHG</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -41859,7 +41859,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>(143708) - InterContinental Hanoi Westlake by IHG</t>
+          <t>InterContinental Hanoi Westlake by IHG</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -41904,7 +41904,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -41939,7 +41939,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>(360241) - Holiday Inn Express &amp; Suites Downtown Ottawa East by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Downtown Ottawa East by IHG</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -41949,7 +41949,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -41984,7 +41984,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>(108804) - Kimpton Hotel Eventi by IHG</t>
+          <t>Kimpton Hotel Eventi by IHG</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -41994,7 +41994,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>(101372) - Mahekal Beach Front Resort &amp; Spa</t>
+          <t>Mahekal Beach Front Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -42039,7 +42039,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -42074,7 +42074,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>(547726) - Holiday Inn Express Düsseldorf – Hauptbahnhof by IHG</t>
+          <t>Holiday Inn Express Düsseldorf – Hauptbahnhof by IHG</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -42084,7 +42084,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -42119,7 +42119,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>(231691) - SAHARA Las Vegas</t>
+          <t>SAHARA Las Vegas</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -42129,7 +42129,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -42164,7 +42164,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>(143373) - Crowne Plaza Danang City Centre by IHG</t>
+          <t>Crowne Plaza Danang City Centre by IHG</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -42174,7 +42174,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -42209,7 +42209,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>(311431) - Hyatt Regency Cartagena</t>
+          <t>Hyatt Regency Cartagena</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -42219,7 +42219,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>(101629) - Secrets Maroma Beach Riviera Cancun - Solo Adultos</t>
+          <t>Secrets Maroma Beach Riviera Cancun - Solo Adultos</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -42264,7 +42264,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -42299,7 +42299,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>(126531) - Hyatt Regency Huntington Beach Resort and Spa</t>
+          <t>Hyatt Regency Huntington Beach Resort and Spa</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -42309,7 +42309,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -42344,7 +42344,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>(550407) - Hotel Indigo PANAMA CITY MARINA by IHG</t>
+          <t>Hotel Indigo PANAMA CITY MARINA by IHG</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -42354,7 +42354,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -42389,7 +42389,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>(120074) - Crowne Plaza Paris Republique by IHG</t>
+          <t>Crowne Plaza Paris Republique by IHG</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -42399,7 +42399,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -42434,7 +42434,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>(208877) - Holiday Inn Panama Distrito Financiero by IHG</t>
+          <t>Holiday Inn Panama Distrito Financiero by IHG</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -42444,7 +42444,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -42479,7 +42479,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>(100078) - Posada Real Puerto Escondido</t>
+          <t>Posada Real Puerto Escondido</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -42489,7 +42489,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -42524,7 +42524,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>(547780) - Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
+          <t>Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -42534,7 +42534,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -42569,7 +42569,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>(111284) - Hyatt Regency Denver Tech Center</t>
+          <t>Hyatt Regency Denver Tech Center</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -42579,7 +42579,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -42614,7 +42614,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>(114325) - Crowne Plaza London - Kings Cross by IHG</t>
+          <t>Crowne Plaza London - Kings Cross by IHG</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -42624,7 +42624,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -42659,7 +42659,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>(127435) - InterContinental Istanbul by IHG</t>
+          <t>InterContinental Istanbul by IHG</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -42669,7 +42669,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -42704,7 +42704,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>(143321) - InterContinental Danang Sun Peninsula Resort by IHG</t>
+          <t>InterContinental Danang Sun Peninsula Resort by IHG</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -42749,7 +42749,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>(107809) - Holiday Inn Washington-Central/White House by IHG</t>
+          <t>Holiday Inn Washington-Central/White House by IHG</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -42759,7 +42759,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61265,7 +61265,7 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61353,7 +61353,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>(100091) - All Ritmo Cancún Resort &amp; Waterpark</t>
+          <t>All Ritmo Cancún Resort &amp; Waterpark</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -61363,7 +61363,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -61395,7 +61395,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>(100699) - Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
+          <t>Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -61405,7 +61405,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -61437,7 +61437,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>(104094) - Hotel Almirante Cartagena</t>
+          <t>Hotel Almirante Cartagena</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -61447,7 +61447,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -61479,7 +61479,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>(404605) - Hyatt Place Marlborough/Apex Center</t>
+          <t>Hyatt Place Marlborough/Apex Center</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -61489,7 +61489,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -61521,7 +61521,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>(153885) - Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -61531,7 +61531,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -61563,7 +61563,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>(481765) - Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
+          <t>Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -61573,7 +61573,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -61605,7 +61605,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>(324901) - Paris Las Vegas Resort &amp; Casino</t>
+          <t>Paris Las Vegas Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -61615,7 +61615,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -61647,7 +61647,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>(160813) - Holiday Inn Express Portland West/Hillsboro by IHG</t>
+          <t>Holiday Inn Express Portland West/Hillsboro by IHG</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -61657,7 +61657,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -61689,7 +61689,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>(102834) - Holiday Inn Santo Domingo</t>
+          <t>Holiday Inn Santo Domingo</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -61699,7 +61699,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -61731,7 +61731,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>(103579) - Caribe Royale Orlando</t>
+          <t>Caribe Royale Orlando</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -61741,7 +61741,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -61773,7 +61773,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>(252206) - Hyatt Centric The Loop Chicago</t>
+          <t>Hyatt Centric The Loop Chicago</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -61783,7 +61783,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -61815,7 +61815,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>(547672) - Hotel Indigo TOKYO SHIBUYA by IHG</t>
+          <t>Hotel Indigo TOKYO SHIBUYA by IHG</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -61825,7 +61825,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -61857,7 +61857,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>(155801) - Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -61867,7 +61867,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -61899,7 +61899,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>(188728) - ANA InterContinental Ishigaki Resort by IHG</t>
+          <t>ANA InterContinental Ishigaki Resort by IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -61909,7 +61909,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -61941,7 +61941,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>(111210) - Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
+          <t>Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -61951,7 +61951,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -61983,7 +61983,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>(135880) - Crowne Plaza Limassol by IHG</t>
+          <t>Crowne Plaza Limassol by IHG</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -61993,7 +61993,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -62025,7 +62025,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>(306731) - Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -62035,7 +62035,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -62067,7 +62067,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>(162083) - Tropicana Laughlin</t>
+          <t>Tropicana Laughlin</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -62077,7 +62077,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -62109,7 +62109,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>(109744) - Holiday Inn NYC - Lower East Side by IHG</t>
+          <t>Holiday Inn NYC - Lower East Side by IHG</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -62119,7 +62119,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -62151,7 +62151,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>(319646) - Grand Hyatt Bogota</t>
+          <t>Grand Hyatt Bogota</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -62161,7 +62161,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -62193,7 +62193,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>(120946) - voco Dubai by IHG</t>
+          <t>voco Dubai by IHG</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -62203,7 +62203,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -62235,7 +62235,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>(479128) - La Mer Resort &amp; Spa Crete</t>
+          <t>La Mer Resort &amp; Spa Crete</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -62245,7 +62245,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -62277,7 +62277,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>(167825) - Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -62287,7 +62287,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>(227892) - Holiday Inn Express London Wandsworth by IHG</t>
+          <t>Holiday Inn Express London Wandsworth by IHG</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -62329,7 +62329,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -62361,7 +62361,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>(154983) - Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -62371,7 +62371,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -62403,7 +62403,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>(104963) - Sofitel New York</t>
+          <t>Sofitel New York</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -62413,7 +62413,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -62445,7 +62445,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>(100371) - Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
+          <t>Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -62455,7 +62455,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -62487,7 +62487,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>(322551) - Ocean El Faro</t>
+          <t>Ocean El Faro</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -62497,7 +62497,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -62529,7 +62529,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>(267834) - Holiday Inn Express - Edinburgh City Centre by IHG</t>
+          <t>Holiday Inn Express - Edinburgh City Centre by IHG</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -62539,7 +62539,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -62571,7 +62571,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>(481271) - Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
+          <t>Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -62581,7 +62581,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -62613,7 +62613,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>(107811) - Hyatt Regency Washington on Capitol Hill</t>
+          <t>Hyatt Regency Washington on Capitol Hill</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -62623,7 +62623,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -62655,7 +62655,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>(425153) - Hotel Indigo London - 1 Leicester Square by IHG</t>
+          <t>Hotel Indigo London - 1 Leicester Square by IHG</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -62665,7 +62665,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -62697,7 +62697,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>(111030) - Holiday Inn Express New York - Manhattan West Side by IHG</t>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -62707,7 +62707,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -62739,7 +62739,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>(219851) - Holiday Inn Bristol City Centre by IHG</t>
+          <t>Holiday Inn Bristol City Centre by IHG</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -62749,7 +62749,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -62781,7 +62781,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>(506020) - Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -62791,7 +62791,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -62823,7 +62823,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>(136246) - Holiday Inn Tbilisi by IHG</t>
+          <t>Holiday Inn Tbilisi by IHG</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -62833,7 +62833,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -62865,7 +62865,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>(165366) - Crowne Plaza College Park - Washington DC by IHG</t>
+          <t>Crowne Plaza College Park - Washington DC by IHG</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -62875,7 +62875,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -62907,7 +62907,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>(123825) - Hotel Indigo Glasgow by IHG</t>
+          <t>Hotel Indigo Glasgow by IHG</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -62917,7 +62917,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -62949,7 +62949,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>(283467) - Holiday Inn Express London - ExCeL by IHG</t>
+          <t>Holiday Inn Express London - ExCeL by IHG</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -62959,7 +62959,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -62991,7 +62991,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>(105159) - Crowne Plaza Newark Airport by IHG</t>
+          <t>Crowne Plaza Newark Airport by IHG</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -63001,7 +63001,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -63033,7 +63033,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>(492790) - Holiday Inn Express Liverpool Central by IHG</t>
+          <t>Holiday Inn Express Liverpool Central by IHG</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -63043,7 +63043,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -63075,7 +63075,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>(107757) - Kimpton Theta New York - Times Square by IHG</t>
+          <t>Kimpton Theta New York - Times Square by IHG</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -63085,7 +63085,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -63117,7 +63117,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>(108804) - Kimpton Hotel Eventi by IHG</t>
+          <t>Kimpton Hotel Eventi by IHG</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -63127,7 +63127,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -63159,7 +63159,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>(101372) - Mahekal Beach Front Resort &amp; Spa</t>
+          <t>Mahekal Beach Front Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -63169,7 +63169,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -63201,7 +63201,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>(231691) - SAHARA Las Vegas</t>
+          <t>SAHARA Las Vegas</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -63211,7 +63211,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -63243,7 +63243,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>(143373) - Crowne Plaza Danang City Centre by IHG</t>
+          <t>Crowne Plaza Danang City Centre by IHG</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -63253,7 +63253,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -63285,7 +63285,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>(311431) - Hyatt Regency Cartagena</t>
+          <t>Hyatt Regency Cartagena</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -63295,7 +63295,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -63327,7 +63327,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>(126531) - Hyatt Regency Huntington Beach Resort and Spa</t>
+          <t>Hyatt Regency Huntington Beach Resort and Spa</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -63337,7 +63337,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -63369,7 +63369,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>(550407) - Hotel Indigo PANAMA CITY MARINA by IHG</t>
+          <t>Hotel Indigo PANAMA CITY MARINA by IHG</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -63379,7 +63379,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -63411,7 +63411,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>(208877) - Holiday Inn Panama Distrito Financiero by IHG</t>
+          <t>Holiday Inn Panama Distrito Financiero by IHG</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -63421,7 +63421,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -63453,7 +63453,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>(547780) - Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
+          <t>Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -63463,7 +63463,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -63495,7 +63495,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>(143321) - InterContinental Danang Sun Peninsula Resort by IHG</t>
+          <t>InterContinental Danang Sun Peninsula Resort by IHG</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -63505,7 +63505,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -63537,7 +63537,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>(547881) - Holiday Inn Resort BALI CANGGU by IHG</t>
+          <t>Holiday Inn Resort BALI CANGGU by IHG</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -63547,7 +63547,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -63579,7 +63579,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>(160374) - Crowne Plaza Providence-Warwick Airport by IHG</t>
+          <t>Crowne Plaza Providence-Warwick Airport by IHG</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -63589,7 +63589,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -63621,7 +63621,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>(402847) - Holiday Inn &amp; Suites Philadelphia W - Drexel Hill by IHG</t>
+          <t>Holiday Inn &amp; Suites Philadelphia W - Drexel Hill by IHG</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -63631,7 +63631,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -63663,7 +63663,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>(115245) - Hyatt Regency La Jolla</t>
+          <t>Hyatt Regency La Jolla</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -63673,7 +63673,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -63705,7 +63705,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>(425767) - EVEN Hotel Seattle Downtown - Lake Union by IHG</t>
+          <t>EVEN Hotel Seattle Downtown - Lake Union by IHG</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -63715,7 +63715,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -63747,7 +63747,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>(154994) - Days Inn by Wyndham Edmundston</t>
+          <t>Days Inn by Wyndham Edmundston</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -63757,7 +63757,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -63789,7 +63789,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>(103292) - Holiday Inn Austin Midtown by IHG</t>
+          <t>Holiday Inn Austin Midtown by IHG</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -63799,7 +63799,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -63831,7 +63831,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>(103694) - Manchester Grand Hyatt San Diego</t>
+          <t>Manchester Grand Hyatt San Diego</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -63841,7 +63841,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -63873,7 +63873,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>(111417) - InterContinental London Park Lane by IHG</t>
+          <t>InterContinental London Park Lane by IHG</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -63883,7 +63883,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -63915,7 +63915,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>(154772) - Holiday Inn Express Hotel &amp; Suites CLARINGTON - BOWMANVILLE by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites CLARINGTON - BOWMANVILLE by IHG</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -63925,7 +63925,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -63957,7 +63957,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>(131468) - Hyatt Regency Orlando</t>
+          <t>Hyatt Regency Orlando</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -63967,7 +63967,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -63999,7 +63999,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>(276943) - Waldorf Astoria Dubai Palm Jumeirah</t>
+          <t>Waldorf Astoria Dubai Palm Jumeirah</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -64009,7 +64009,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -64041,7 +64041,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>(493347) - Hotel Indigo Bali Seminyak Beach by IHG</t>
+          <t>Hotel Indigo Bali Seminyak Beach by IHG</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -64051,7 +64051,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -64083,7 +64083,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>(153326) - Holiday Inn Express Edmonton Downtown by IHG</t>
+          <t>Holiday Inn Express Edmonton Downtown by IHG</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -64093,7 +64093,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -64125,7 +64125,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>(110720) - Crowne Plaza Dallas Market Ctr - Love Field by IHG</t>
+          <t>Crowne Plaza Dallas Market Ctr - Love Field by IHG</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -64135,7 +64135,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -64167,7 +64167,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>(120830) - Crowne Plaza Portland Downtown Convention Center by IHG</t>
+          <t>Crowne Plaza Portland Downtown Convention Center by IHG</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -64177,7 +64177,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -64209,7 +64209,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>(186668) - Holiday Inn Key Largo by IHG</t>
+          <t>Holiday Inn Key Largo by IHG</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -64219,7 +64219,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -64251,7 +64251,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>(182511) - Holiday Inn &amp; Suites Ocean City by IHG</t>
+          <t>Holiday Inn &amp; Suites Ocean City by IHG</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -64261,7 +64261,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -64293,7 +64293,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>(541116) - InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa by IHG</t>
+          <t>InterContinental Ras Al Khaimah Mina Al Arab Resort &amp; Spa by IHG</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -64303,7 +64303,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -64335,7 +64335,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>(218642) - Holiday Inn Oxford by IHG</t>
+          <t>Holiday Inn Oxford by IHG</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -64345,7 +64345,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -64377,7 +64377,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>(159373) - Holiday Inn Express Hotel &amp; Suites Clearwater/Us 19 N by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Clearwater/Us 19 N by IHG</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -64387,7 +64387,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -64419,7 +64419,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>(463769) - Holiday Inn Express New Rochelle by IHG</t>
+          <t>Holiday Inn Express New Rochelle by IHG</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -64429,7 +64429,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -64461,7 +64461,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>(105630) - Holiday Inn Resort Aruba</t>
+          <t>Holiday Inn Resort Aruba</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -64471,7 +64471,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -64503,7 +64503,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>(102602) - Holiday Inn Express New York City- Wall Street by IHG</t>
+          <t>Holiday Inn Express New York City- Wall Street by IHG</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -64513,7 +64513,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -64545,7 +64545,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>(481289) - Holiday Inn FRANKFURT AIRPORT by IHG</t>
+          <t>Holiday Inn FRANKFURT AIRPORT by IHG</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -64555,7 +64555,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -64587,7 +64587,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>(116694) - Grand Hyatt Athens</t>
+          <t>Grand Hyatt Athens</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -64597,7 +64597,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -64629,7 +64629,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>(165902) - Holiday Inn Express &amp; Suites Galveston West-Seawall</t>
+          <t>Holiday Inn Express &amp; Suites Galveston West-Seawall</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -64639,7 +64639,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -64671,7 +64671,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>(154042) - Holiday Inn Oakville Centre by IHG</t>
+          <t>Holiday Inn Oakville Centre by IHG</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -64681,7 +64681,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -64713,7 +64713,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>(103717) - Hyatt Regency London The Churchill</t>
+          <t>Hyatt Regency London The Churchill</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -64723,7 +64723,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -64755,7 +64755,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>(102019) - Eden Roc Miami Beach</t>
+          <t>Eden Roc Miami Beach</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -64765,7 +64765,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -64797,7 +64797,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>(241829) - Holiday Inn Express &amp; Suites Bogota Zona Financiera</t>
+          <t>Holiday Inn Express &amp; Suites Bogota Zona Financiera</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -64807,7 +64807,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -64839,7 +64839,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>(479990) - Fontainebleau Las Vegas, MICHELIN Key Award Hotel</t>
+          <t>Fontainebleau Las Vegas, MICHELIN Key Award Hotel</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -64849,7 +64849,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -64881,7 +64881,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>(250896) - Holiday Inn Houston Downtown by IHG</t>
+          <t>Holiday Inn Houston Downtown by IHG</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -64891,7 +64891,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -64923,7 +64923,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>(111034) - Holiday Inn Manhattan 6th Ave - Chelsea by IHG</t>
+          <t>Holiday Inn Manhattan 6th Ave - Chelsea by IHG</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -64933,7 +64933,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -64965,7 +64965,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>(131583) - Holiday Inn Express Toronto - Downtown by IHG</t>
+          <t>Holiday Inn Express Toronto - Downtown by IHG</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -64975,7 +64975,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -65007,7 +65007,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>(104932) - Holiday Inn Montréal Centre-Ville Downtown by IHG</t>
+          <t>Holiday Inn Montréal Centre-Ville Downtown by IHG</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -65017,7 +65017,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -65049,7 +65049,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>(267012) - Crowne Plaza Liverpool City Centre by IHG</t>
+          <t>Crowne Plaza Liverpool City Centre by IHG</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -65059,7 +65059,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -65091,7 +65091,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>(160419) - Holiday Inn Boston - Dedham Hotel &amp; Conference Center by IHG</t>
+          <t>Holiday Inn Boston - Dedham Hotel &amp; Conference Center by IHG</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -65101,7 +65101,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -65133,7 +65133,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>(441425) - Fairmont Century Plaza Los Angeles at Beverly Hills</t>
+          <t>Fairmont Century Plaza Los Angeles at Beverly Hills</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -65143,7 +65143,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -65175,7 +65175,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>(108551) - Holiday Inn Express &amp; Suites Boston - Cambridge by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Boston - Cambridge by IHG</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -65185,7 +65185,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -65217,7 +65217,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>(110927) - Andaz Miami Beach Resort &amp; Spa</t>
+          <t>Andaz Miami Beach Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -65227,7 +65227,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -65259,7 +65259,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>(172260) - Hyatt Regency Minneapolis</t>
+          <t>Hyatt Regency Minneapolis</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -65269,7 +65269,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -65301,7 +65301,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>(547660) - voco OSAKA CENTRAL by IHG</t>
+          <t>voco OSAKA CENTRAL by IHG</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -65311,7 +65311,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -65343,7 +65343,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>(111042) - Hyatt Regency Jersey City on the Hudson</t>
+          <t>Hyatt Regency Jersey City on the Hudson</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -65353,7 +65353,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -65385,7 +65385,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>(219047) - Holiday Inn Cardiff City Centre by IHG</t>
+          <t>Holiday Inn Cardiff City Centre by IHG</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -65395,7 +65395,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -65427,7 +65427,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>(267264) - Crowne Plaza Plymouth by IHG</t>
+          <t>Crowne Plaza Plymouth by IHG</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -65437,7 +65437,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -65469,7 +65469,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>(117568) - Holiday Inn Express Madrid - Getafe by IHG</t>
+          <t>Holiday Inn Express Madrid - Getafe by IHG</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -65479,7 +65479,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -65511,7 +65511,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>(111836) - Grand Hyatt Barcelona</t>
+          <t>Grand Hyatt Barcelona</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -65521,7 +65521,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -65564,7 +65564,7 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="37" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65646,7 +65646,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>(102044) - Fairmont San Francisco</t>
+          <t>Fairmont San Francisco</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -65656,7 +65656,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -65685,7 +65685,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>(103819) - Iberostar Selection Rose Hall Suites</t>
+          <t>Iberostar Selection Rose Hall Suites</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -65695,7 +65695,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -65724,7 +65724,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>(112571) - Melia White House</t>
+          <t>Melia White House</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -65734,7 +65734,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -65763,7 +65763,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>(417269) - ibis budget Barranquilla</t>
+          <t>ibis budget Barranquilla</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -65773,7 +65773,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -65802,7 +65802,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>(238963) - Krystal Monterrey</t>
+          <t>Krystal Monterrey</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -65812,7 +65812,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -65841,7 +65841,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>(471666) - Las Vegas Hilton at Resorts World</t>
+          <t>Las Vegas Hilton at Resorts World</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -65851,7 +65851,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -65880,7 +65880,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>(311175) - Hotel Exe Bacatá 95</t>
+          <t>Hotel Exe Bacatá 95</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -65890,7 +65890,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -65919,7 +65919,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>(475706) - Conrad Las Vegas at Resorts World</t>
+          <t>Conrad Las Vegas at Resorts World</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -65929,7 +65929,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -65958,7 +65958,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>(310158) - Hyatt House Irvine/John Wayne Airport</t>
+          <t>Hyatt House Irvine/John Wayne Airport</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -65968,7 +65968,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -65997,7 +65997,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>(174968) - Andaz Maui at Wailea Resort - a concept by Hyatt</t>
+          <t>Andaz Maui at Wailea Resort - a concept by Hyatt</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -66007,7 +66007,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -66036,7 +66036,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>(103516) - Hotel Dann Avenida 19 Bogotá</t>
+          <t>Hotel Dann Avenida 19 Bogotá</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -66046,7 +66046,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -66075,7 +66075,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>(558700) - Fairmont Tokyo</t>
+          <t>Fairmont Tokyo</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -66085,7 +66085,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -66114,7 +66114,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>(121787) - Holiday Inn Cairo Maadi by IHG</t>
+          <t>Holiday Inn Cairo Maadi by IHG</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -66124,7 +66124,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -66153,7 +66153,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>(258252) - Holiday Inn Express &amp; Suites Phoenix West - Buckeye by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Phoenix West - Buckeye by IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -66163,7 +66163,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -66192,7 +66192,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>(213505) - Holiday Inn Express &amp; Suites Montgomery by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Montgomery by IHG</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -66202,7 +66202,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -66231,7 +66231,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>(117874) - The Ritz-Carlton, Naples</t>
+          <t>The Ritz-Carlton, Naples</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -66241,7 +66241,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -66270,7 +66270,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>(309176) - Hotel Indigo Los Angeles Downtown by IHG</t>
+          <t>Hotel Indigo Los Angeles Downtown by IHG</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -66280,7 +66280,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -66309,7 +66309,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>(547707) - Holiday Inn - the niu, LOCO MUNICH NORTH by IHG</t>
+          <t>Holiday Inn - the niu, LOCO MUNICH NORTH by IHG</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -66319,7 +66319,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -66348,7 +66348,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>(109522) - InterContinental Barcelona by IHG</t>
+          <t>InterContinental Barcelona by IHG</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -66358,7 +66358,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -66387,7 +66387,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>(161310) - Candlewood Suites Anaheim - Resort Area by IHG</t>
+          <t>Candlewood Suites Anaheim - Resort Area by IHG</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -66397,7 +66397,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -66426,7 +66426,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>(237571) - Secrets Akumal Riviera Maya</t>
+          <t>Secrets Akumal Riviera Maya</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -66436,7 +66436,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -66465,7 +66465,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>(103348) - The Westin Bonaventure Hotel and Suites, Los Angeles</t>
+          <t>The Westin Bonaventure Hotel and Suites, Los Angeles</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -66475,7 +66475,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -66504,7 +66504,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>(120716) - Hilton Garden Inn Nashville Vanderbilt</t>
+          <t>Hilton Garden Inn Nashville Vanderbilt</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -66514,7 +66514,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -66543,7 +66543,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>(101760) - Hard Rock Hotel Riviera Maya</t>
+          <t>Hard Rock Hotel Riviera Maya</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -66553,7 +66553,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -66582,7 +66582,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>(111987) - Novotel Muenchen City</t>
+          <t>Novotel Muenchen City</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -66592,7 +66592,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -66621,7 +66621,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>(114237) - Crowne Plaza San Francisco Airport by IHG</t>
+          <t>Crowne Plaza San Francisco Airport by IHG</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -66631,7 +66631,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -66660,7 +66660,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>(182542) - Holiday Inn Ocean City by IHG</t>
+          <t>Holiday Inn Ocean City by IHG</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -66670,7 +66670,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -66699,7 +66699,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>(172179) - InterContinental Saint Paul Riverfront by IHG</t>
+          <t>InterContinental Saint Paul Riverfront by IHG</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -66709,7 +66709,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -66738,7 +66738,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>(101001) - Fiesta Americana Condesa Cancún All Inclusive</t>
+          <t>Fiesta Americana Condesa Cancún All Inclusive</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -66748,7 +66748,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -66777,7 +66777,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>(209082) - Secrets Playa Mujeres Golf and Resort - All Inclusive Adults Only</t>
+          <t>Secrets Playa Mujeres Golf and Resort - All Inclusive Adults Only</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -66787,7 +66787,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -66816,7 +66816,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>(492803) - Thompson Madrid, by Hyatt</t>
+          <t>Thompson Madrid, by Hyatt</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -66826,7 +66826,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -66855,7 +66855,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>(102792) - Parc 55 San Francisco - A Hilton Hotel</t>
+          <t>Parc 55 San Francisco - A Hilton Hotel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -66865,7 +66865,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -66894,7 +66894,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>(106053) - Pullman São Paulo Guarulhos Airport</t>
+          <t>Pullman São Paulo Guarulhos Airport</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -66904,7 +66904,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -66933,7 +66933,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>(280140) - Hilton Batumi</t>
+          <t>Hilton Batumi</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -66943,7 +66943,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -66972,7 +66972,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>(196366) - Holiday Inn Nice by IHG</t>
+          <t>Holiday Inn Nice by IHG</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -66982,7 +66982,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -67011,7 +67011,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>(139888) - InterContinental Jeddah by IHG</t>
+          <t>InterContinental Jeddah by IHG</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -67021,7 +67021,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -67050,7 +67050,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>(105164) - Holiday Inn Newark International Airport by IHG</t>
+          <t>Holiday Inn Newark International Airport by IHG</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -67060,7 +67060,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -67089,7 +67089,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>(107533) - Holiday Inn Express NYC Chelsea – NoMad Area by IHG</t>
+          <t>Holiday Inn Express NYC Chelsea – NoMad Area by IHG</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -67099,7 +67099,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -67128,7 +67128,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>(105369) - Holiday Inn Santiago - Airport Terminal by IHG</t>
+          <t>Holiday Inn Santiago - Airport Terminal by IHG</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -67138,7 +67138,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -67167,7 +67167,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>(153455) - Holiday Inn &amp; Suites Montreal Airport by IHG</t>
+          <t>Holiday Inn &amp; Suites Montreal Airport by IHG</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -67177,7 +67177,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -67206,7 +67206,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>(118506) - Best Western Amsterdam</t>
+          <t>Best Western Amsterdam</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -67216,7 +67216,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -67245,7 +67245,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>(103363) - The Manhattan at Times Square Hotel</t>
+          <t>The Manhattan at Times Square Hotel</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -67255,7 +67255,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -67284,7 +67284,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>(108549) - Wyndham Boston Beacon Hill</t>
+          <t>Wyndham Boston Beacon Hill</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -67294,7 +67294,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -67323,7 +67323,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>(104797) - Crowne Plaza Toronto Airport by IHG</t>
+          <t>Crowne Plaza Toronto Airport by IHG</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -67333,7 +67333,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -67362,7 +67362,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>(105107) - TRYP by Wyndham New York City Times Square / Midtown</t>
+          <t>TRYP by Wyndham New York City Times Square / Midtown</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -67372,7 +67372,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -67401,7 +67401,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>(103365) - Sheraton New York Times Square Hotel</t>
+          <t>Sheraton New York Times Square Hotel</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -67411,7 +67411,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -67440,7 +67440,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>(455621) - Holiday Inn &amp; Suites Idaho Falls by IHG</t>
+          <t>Holiday Inn &amp; Suites Idaho Falls by IHG</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -67450,7 +67450,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -67479,7 +67479,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>(169458) - The Scottsdale Resort and Spa, Curio Collection by Hilton</t>
+          <t>The Scottsdale Resort and Spa, Curio Collection by Hilton</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -67489,7 +67489,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -67518,7 +67518,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>(120312) - Fairmont Olympic Hotel</t>
+          <t>Fairmont Olympic Hotel</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -67528,7 +67528,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -67557,7 +67557,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>(239623) - Hyatt Place New York/Yonkers</t>
+          <t>Hyatt Place New York/Yonkers</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -67567,7 +67567,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -67596,7 +67596,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>(179244) - Hilton Myrtle Beach Resort</t>
+          <t>Hilton Myrtle Beach Resort</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -67606,7 +67606,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -67635,7 +67635,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>(218461) - Crowne Plaza Harrogate by IHG</t>
+          <t>Crowne Plaza Harrogate by IHG</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -67645,7 +67645,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -67674,7 +67674,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>(200277) - Hôtel du Palais Biarritz, in The Unbound Collection by Hyatt</t>
+          <t>Hôtel du Palais Biarritz, in The Unbound Collection by Hyatt</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -67684,7 +67684,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -67713,7 +67713,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>(257872) - Hotel Indigo Atlanta Downtown by IHG</t>
+          <t>Hotel Indigo Atlanta Downtown by IHG</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -67723,7 +67723,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -67752,7 +67752,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>(105194) - Best Western Plus Downtown Inn &amp; Suites</t>
+          <t>Best Western Plus Downtown Inn &amp; Suites</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -67762,7 +67762,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -67791,7 +67791,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>(107534) - Holiday Inn New York City - Wall Street by IHG</t>
+          <t>Holiday Inn New York City - Wall Street by IHG</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -67801,7 +67801,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -67830,7 +67830,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>(107551) - voco Surfside Aruba by IHG</t>
+          <t>voco Surfside Aruba by IHG</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -67840,7 +67840,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -67869,7 +67869,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>(168158) - Crowne Plaza Atlanta NE - Norcross by IHG</t>
+          <t>Crowne Plaza Atlanta NE - Norcross by IHG</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -67879,7 +67879,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -67908,7 +67908,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>(103474) - Universal's Loews Portofino Bay Hotel</t>
+          <t>Universal's Loews Portofino Bay Hotel</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -67918,7 +67918,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -67947,7 +67947,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>(118884) - Crowne Plaza Boston - Woburn by IHG</t>
+          <t>Crowne Plaza Boston - Woburn by IHG</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -67957,7 +67957,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -67986,7 +67986,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>(239578) - Hotel Indigo Lower East Side New York by IHG</t>
+          <t>Hotel Indigo Lower East Side New York by IHG</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -67996,7 +67996,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -68025,7 +68025,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>(103378) - InterContinental New York Times Square by IHG</t>
+          <t>InterContinental New York Times Square by IHG</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -68035,7 +68035,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -68064,7 +68064,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>(104809) - Hyatt Regency Toronto</t>
+          <t>Hyatt Regency Toronto</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -68074,7 +68074,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -68103,7 +68103,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>(102638) - Ramada by Wyndham Kissimmee Gateway</t>
+          <t>Ramada by Wyndham Kissimmee Gateway</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -68113,7 +68113,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -68142,7 +68142,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>(174772) - DoubleTree by Hilton Sonoma - Wine Country</t>
+          <t>DoubleTree by Hilton Sonoma - Wine Country</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -68152,7 +68152,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -68181,7 +68181,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>(124784) - Marriott Marquis San Diego Marina</t>
+          <t>Marriott Marquis San Diego Marina</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -68191,7 +68191,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -68220,7 +68220,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>(108555) - Hyatt Regency Boston/Cambridge</t>
+          <t>Hyatt Regency Boston/Cambridge</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -68230,7 +68230,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -68259,7 +68259,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>(238929) - Dreams Playa Mujeres Golf &amp; Spa Resort</t>
+          <t>Dreams Playa Mujeres Golf &amp; Spa Resort</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -68269,7 +68269,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -68298,7 +68298,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>(110666) - Crowne Plaza Orlando - Downtown by IHG</t>
+          <t>Crowne Plaza Orlando - Downtown by IHG</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -68308,7 +68308,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -68337,7 +68337,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>(108294) - InterContinental New Orleans by IHG</t>
+          <t>InterContinental New Orleans by IHG</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -68347,7 +68347,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -68376,7 +68376,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>(113861) - Peachtree Hotel Midtown Atlanta</t>
+          <t>Peachtree Hotel Midtown Atlanta</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -68386,7 +68386,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -68415,7 +68415,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>(103850) - Pullman Paris Montparnasse Hotel</t>
+          <t>Pullman Paris Montparnasse Hotel</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -68425,7 +68425,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -68454,7 +68454,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>(103856) - Novotel London West</t>
+          <t>Novotel London West</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -68464,7 +68464,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -68493,7 +68493,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>(107553) - DoubleTree by Hilton New York Downtown</t>
+          <t>DoubleTree by Hilton New York Downtown</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -68503,7 +68503,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -68532,7 +68532,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>(519727) - Courtyard by Marriott Brisbane South Bank</t>
+          <t>Courtyard by Marriott Brisbane South Bank</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -68542,7 +68542,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Expedia</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -68571,7 +68571,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>(218922) - DoubleTree by Hilton Hotel Bristol South - Cadbury House</t>
+          <t>DoubleTree by Hilton Hotel Bristol South - Cadbury House</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -68581,7 +68581,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -68610,7 +68610,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>(107881) - Ocean Blue &amp; Sand Beach Resort</t>
+          <t>Ocean Blue &amp; Sand Beach Resort</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -68620,7 +68620,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -68649,7 +68649,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>(238287) - Waldorf Astoria Los Cabos Pedregal</t>
+          <t>Waldorf Astoria Los Cabos Pedregal</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -68659,7 +68659,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -68688,7 +68688,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>(104790) - Travelodge Hotel by Wyndham Montreal Centre</t>
+          <t>Travelodge Hotel by Wyndham Montreal Centre</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -68698,7 +68698,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -68727,7 +68727,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>(114434) - Mercure Budapest City Center Hotel</t>
+          <t>Mercure Budapest City Center Hotel</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -68737,7 +68737,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -68766,7 +68766,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>(111649) - Travelodge by Wyndham Downtown Chicago</t>
+          <t>Travelodge by Wyndham Downtown Chicago</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -68776,7 +68776,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -68805,7 +68805,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>(483946) - Embassy Suites by Hilton Portland Airport</t>
+          <t>Embassy Suites by Hilton Portland Airport</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -68815,7 +68815,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -68844,7 +68844,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>(484433) - Crowne Plaza Marseille Le Dome by IHG</t>
+          <t>Crowne Plaza Marseille Le Dome by IHG</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -68854,7 +68854,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -68883,7 +68883,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>(103606) - Holiday Inn &amp; Suites Clearwater Beach by IHG</t>
+          <t>Holiday Inn &amp; Suites Clearwater Beach by IHG</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -68893,7 +68893,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -68922,7 +68922,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>(277026) - Hyatt Place Amsterdam Airport</t>
+          <t>Hyatt Place Amsterdam Airport</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -68932,7 +68932,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -68961,7 +68961,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>(157396) - Holiday Inn Boston - Cambridge Area by IHG</t>
+          <t>Holiday Inn Boston - Cambridge Area by IHG</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -68971,7 +68971,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -69000,7 +69000,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>(168184) - Hyatt Regency Atlanta Perimeter at Villa Christina</t>
+          <t>Hyatt Regency Atlanta Perimeter at Villa Christina</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -69010,7 +69010,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -69039,7 +69039,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>(343999) - Hyatt Regency Vienna</t>
+          <t>Hyatt Regency Vienna</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -69049,7 +69049,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -69078,7 +69078,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>(462795) - Athens Capital Center Hotel-MGallery Collection</t>
+          <t>Athens Capital Center Hotel-MGallery Collection</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -69088,7 +69088,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -69117,7 +69117,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>(532452) - Grand Hyatt Izmir Istinyepark</t>
+          <t>Grand Hyatt Izmir Istinyepark</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -69127,7 +69127,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -69156,7 +69156,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>(107957) - Holiday Inn Express Chicago - Magnificent Mile by IHG</t>
+          <t>Holiday Inn Express Chicago - Magnificent Mile by IHG</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -69166,7 +69166,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -69195,7 +69195,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>(116238) - Holiday Inn Baltimore BWI Airport by IHG</t>
+          <t>Holiday Inn Baltimore BWI Airport by IHG</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -69205,7 +69205,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -69234,7 +69234,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>(549924) - Holiday Inn Resort HO TRAM BEACH by IHG</t>
+          <t>Holiday Inn Resort HO TRAM BEACH by IHG</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -69244,7 +69244,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -69273,7 +69273,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>(320024) - Krystal Grand Cancun - All Inclusive</t>
+          <t>Krystal Grand Cancun - All Inclusive</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -69283,7 +69283,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -69312,7 +69312,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>(113785) - Embassy Suites by Hilton Chicago O'Hare Rosemont</t>
+          <t>Embassy Suites by Hilton Chicago O'Hare Rosemont</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -69322,7 +69322,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -69351,7 +69351,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>(112703) - Hyatt Paris Madeleine</t>
+          <t>Hyatt Paris Madeleine</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -69361,7 +69361,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -69390,7 +69390,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>(493380) - Holiday Inn Louisville Downtown by IHG</t>
+          <t>Holiday Inn Louisville Downtown by IHG</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -69400,7 +69400,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -69429,7 +69429,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>(389043) - Ibis Styles Tbilisi Center</t>
+          <t>Ibis Styles Tbilisi Center</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -69439,7 +69439,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -69468,7 +69468,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>(102024) - Kimpton EPIC Hotel by IHG</t>
+          <t>Kimpton EPIC Hotel by IHG</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -69478,7 +69478,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -69507,7 +69507,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>(154227) - Fairmont Tremblant</t>
+          <t>Fairmont Tremblant</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -69517,7 +69517,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -69556,7 +69556,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69650,7 +69650,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="12" t="n">
@@ -69690,7 +69690,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="12" t="n">
@@ -69730,7 +69730,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="12" t="n">
@@ -69770,7 +69770,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="12" t="n">
@@ -69810,7 +69810,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HBSI, HotelBeds, Internal, Siteminder, SynXis, Travelclick</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="12" t="n">
@@ -69850,7 +69850,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
@@ -69890,7 +69890,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
@@ -69930,7 +69930,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
@@ -69970,7 +69970,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
@@ -70010,7 +70010,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
@@ -70050,7 +70050,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="12" t="n">
@@ -70090,7 +70090,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="12" t="n">
@@ -70130,7 +70130,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Expedia, HotelBeds, Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="12" t="n">
@@ -70170,7 +70170,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="12" t="n">
@@ -70210,7 +70210,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft, Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="12" t="n">
@@ -70250,7 +70250,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="12" t="n">
@@ -70290,7 +70290,7 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -70330,7 +70330,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Expedia, Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="12" t="n">
@@ -70370,7 +70370,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
@@ -70410,7 +70410,7 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="12" t="n">
@@ -70450,7 +70450,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
@@ -70490,7 +70490,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Internal, SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="12" t="n">
@@ -70530,7 +70530,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="12" t="n">
@@ -70570,7 +70570,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="12" t="n">
@@ -70610,7 +70610,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="12" t="n">
@@ -70650,7 +70650,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="12" t="n">
@@ -70690,7 +70690,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="12" t="n">
@@ -70730,7 +70730,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="12" t="n">
@@ -70770,7 +70770,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="12" t="n">
@@ -70810,7 +70810,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="12" t="n">
@@ -70850,7 +70850,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="12" t="n">
@@ -70890,7 +70890,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="12" t="n">
@@ -70930,7 +70930,7 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="12" t="n">
@@ -70970,7 +70970,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="12" t="n">
@@ -71010,7 +71010,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="12" t="n">
@@ -71050,7 +71050,7 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D41" s="12" t="n">
@@ -71090,7 +71090,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="12" t="n">
@@ -71130,7 +71130,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="12" t="n">
@@ -71170,7 +71170,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="12" t="n">
@@ -71210,7 +71210,7 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Travelclick</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="12" t="n">
@@ -71250,7 +71250,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="12" t="n">
@@ -71290,7 +71290,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Siteminder</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D47" s="12" t="n">
@@ -71330,7 +71330,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
@@ -71370,7 +71370,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="12" t="n">
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75428,7 +75428,7 @@
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 22:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75516,7 +75516,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>(100091) - All Ritmo Cancún Resort &amp; Waterpark</t>
+          <t>All Ritmo Cancún Resort &amp; Waterpark</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -75526,7 +75526,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -75558,7 +75558,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>(100699) - Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
+          <t>Azul Ixtapa All Inclusive Beach Resort Convention Center</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -75568,7 +75568,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -75600,7 +75600,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>(104094) - Hotel Almirante Cartagena</t>
+          <t>Hotel Almirante Cartagena</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -75610,7 +75610,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -75642,7 +75642,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>(556527) - Masquerade Tower at Rio Hotel</t>
+          <t>Masquerade Tower at Rio Hotel</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -75652,7 +75652,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -75684,7 +75684,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>(450703) - Holiday Inn Express Melbourne Little Collins by IHG</t>
+          <t>Holiday Inn Express Melbourne Little Collins by IHG</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -75694,7 +75694,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -75726,7 +75726,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>(404605) - Hyatt Place Marlborough/Apex Center</t>
+          <t>Hyatt Place Marlborough/Apex Center</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -75736,7 +75736,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -75768,7 +75768,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>(100455) - Paradise Village Beach Resort</t>
+          <t>Paradise Village Beach Resort</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -75778,7 +75778,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -75810,7 +75810,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>(153885) - Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Toronto - Markham by IHG</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -75820,7 +75820,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -75852,7 +75852,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>(104173) - Sol Caribe Sea Flower</t>
+          <t>Sol Caribe Sea Flower</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -75862,7 +75862,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -75894,7 +75894,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>(481765) - Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
+          <t>Holiday Inn Express Osaka City Centre - Midosuji by IHG</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -75904,7 +75904,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -75936,7 +75936,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>(324901) - Paris Las Vegas Resort &amp; Casino</t>
+          <t>Paris Las Vegas Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -75946,7 +75946,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -75978,7 +75978,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>(160813) - Holiday Inn Express Portland West/Hillsboro by IHG</t>
+          <t>Holiday Inn Express Portland West/Hillsboro by IHG</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -75988,7 +75988,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -76020,7 +76020,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>(130860) - ANA InterContinental Manza Beach Resort by IHG</t>
+          <t>ANA InterContinental Manza Beach Resort by IHG</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -76030,7 +76030,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -76062,7 +76062,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>(124195) - Holiday Inn Express Hotel &amp; Suites Meadowlands Area by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites Meadowlands Area by IHG</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -76072,7 +76072,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -76104,7 +76104,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>(102834) - Holiday Inn Santo Domingo</t>
+          <t>Holiday Inn Santo Domingo</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -76114,7 +76114,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -76146,7 +76146,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>(103579) - Caribe Royale Orlando</t>
+          <t>Caribe Royale Orlando</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -76156,7 +76156,7 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -76188,7 +76188,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>(100384) - Meliá Puerto Vallarta All Inclusive</t>
+          <t>Meliá Puerto Vallarta All Inclusive</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -76198,7 +76198,7 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -76230,7 +76230,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>(113476) - Holiday Inn Express London - Croydon by IHG</t>
+          <t>Holiday Inn Express London - Croydon by IHG</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -76240,7 +76240,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -76272,7 +76272,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>(252206) - Hyatt Centric The Loop Chicago</t>
+          <t>Hyatt Centric The Loop Chicago</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -76282,7 +76282,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -76314,7 +76314,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>(547672) - Hotel Indigo TOKYO SHIBUYA by IHG</t>
+          <t>Hotel Indigo TOKYO SHIBUYA by IHG</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -76324,7 +76324,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -76356,7 +76356,7 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>(155801) - Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Detroit North - Troy by IHG</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -76366,7 +76366,7 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -76398,7 +76398,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>(188728) - ANA InterContinental Ishigaki Resort by IHG</t>
+          <t>ANA InterContinental Ishigaki Resort by IHG</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -76408,7 +76408,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -76440,7 +76440,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>(111210) - Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
+          <t>Holiday Inn Express Ft. Lauderdale Cruise-Airport by IHG</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -76450,7 +76450,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -76482,7 +76482,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>(135880) - Crowne Plaza Limassol by IHG</t>
+          <t>Crowne Plaza Limassol by IHG</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -76492,7 +76492,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -76524,7 +76524,7 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>(306731) - Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Montreal Centre-ville Ouest by IHG</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
@@ -76534,7 +76534,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -76566,7 +76566,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>(162083) - Tropicana Laughlin</t>
+          <t>Tropicana Laughlin</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -76576,7 +76576,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>HBSI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -76608,7 +76608,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>(109744) - Holiday Inn NYC - Lower East Side by IHG</t>
+          <t>Holiday Inn NYC - Lower East Side by IHG</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -76618,7 +76618,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -76650,7 +76650,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>(319646) - Grand Hyatt Bogota</t>
+          <t>Grand Hyatt Bogota</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -76660,7 +76660,7 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -76692,7 +76692,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>(120946) - voco Dubai by IHG</t>
+          <t>voco Dubai by IHG</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -76702,7 +76702,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -76734,7 +76734,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>(102609) - Golden Nugget Las Vegas Hotel &amp; Casino</t>
+          <t>Golden Nugget Las Vegas Hotel &amp; Casino</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -76744,7 +76744,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>HotelBeds</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -76776,7 +76776,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>(479128) - La Mer Resort &amp; Spa Crete</t>
+          <t>La Mer Resort &amp; Spa Crete</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -76786,7 +76786,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -76818,7 +76818,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>(167825) - Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
+          <t>Holiday Inn Express Hotel &amp; Suites South Padre Island by IHG</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -76828,7 +76828,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -76860,7 +76860,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>(227892) - Holiday Inn Express London Wandsworth by IHG</t>
+          <t>Holiday Inn Express London Wandsworth by IHG</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -76870,7 +76870,7 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -76902,7 +76902,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>(154983) - Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
+          <t>Holiday Inn Hotel &amp; Suites Osoyoos by IHG</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -76912,7 +76912,7 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -76944,7 +76944,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>(211802) - Voco Gold Coast</t>
+          <t>Voco Gold Coast</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -76954,7 +76954,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -76986,7 +76986,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>(104963) - Sofitel New York</t>
+          <t>Sofitel New York</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -76996,7 +76996,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -77028,7 +77028,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>(111976) - Holiday Inn Munich - South by IHG</t>
+          <t>Holiday Inn Munich - South by IHG</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -77038,7 +77038,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -77070,7 +77070,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>(307905) - Holiday Inn Express &amp; Suites Lancaster East - Strasburg by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Lancaster East - Strasburg by IHG</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -77080,7 +77080,7 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -77112,7 +77112,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>(309593) - Holiday Inn Express &amp; Suites Orlando at SeaWorld by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Orlando at SeaWorld by IHG</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -77122,7 +77122,7 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -77154,7 +77154,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>(129761) - InterContinental Osaka by IHG</t>
+          <t>InterContinental Osaka by IHG</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -77164,7 +77164,7 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -77196,7 +77196,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>(100371) - Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
+          <t>Marival Emotions Resort &amp; Suites Riviera Nayarit by Mercure</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -77206,7 +77206,7 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -77238,7 +77238,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>(158151) - Holiday Inn Kansas City Downtown by IHG</t>
+          <t>Holiday Inn Kansas City Downtown by IHG</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -77248,7 +77248,7 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -77280,7 +77280,7 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>(322551) - Ocean El Faro</t>
+          <t>Ocean El Faro</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
@@ -77290,7 +77290,7 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -77322,7 +77322,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>(267834) - Holiday Inn Express - Edinburgh City Centre by IHG</t>
+          <t>Holiday Inn Express - Edinburgh City Centre by IHG</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -77332,7 +77332,7 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -77364,7 +77364,7 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>(128412) - InterContinental Sydney by IHG</t>
+          <t>InterContinental Sydney by IHG</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -77374,7 +77374,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -77406,7 +77406,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>(100468) - Playa Suites Acapulco</t>
+          <t>Playa Suites Acapulco</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -77416,7 +77416,7 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -77448,7 +77448,7 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>(481271) - Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
+          <t>Holiday Inn Dusseldorf City Toulouser Allee by IHG</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -77458,7 +77458,7 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -77490,7 +77490,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>(114442) - Crowne Plaza Budapest by IHG</t>
+          <t>Crowne Plaza Budapest by IHG</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -77500,7 +77500,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -77532,7 +77532,7 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>(211749) - Crowne Plaza Surfers Paradise by IHG</t>
+          <t>Crowne Plaza Surfers Paradise by IHG</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -77542,7 +77542,7 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -77574,7 +77574,7 @@
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>(113331) - Holiday Inn London-Bloomsbury Hotel by IHG</t>
+          <t>Holiday Inn London-Bloomsbury Hotel by IHG</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -77584,7 +77584,7 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -77616,7 +77616,7 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>(107811) - Hyatt Regency Washington on Capitol Hill</t>
+          <t>Hyatt Regency Washington on Capitol Hill</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -77626,7 +77626,7 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -77658,7 +77658,7 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>(425153) - Hotel Indigo London - 1 Leicester Square by IHG</t>
+          <t>Hotel Indigo London - 1 Leicester Square by IHG</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -77668,7 +77668,7 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -77700,7 +77700,7 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>(116629) - Embassy Suites by Hilton Philadelphia Airport</t>
+          <t>Embassy Suites by Hilton Philadelphia Airport</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -77710,7 +77710,7 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -77742,7 +77742,7 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>(107736) - Embassy Suites by Hilton Orlando Airport</t>
+          <t>Embassy Suites by Hilton Orlando Airport</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -77752,7 +77752,7 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -77784,7 +77784,7 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>(111030) - Holiday Inn Express New York - Manhattan West Side by IHG</t>
+          <t>Holiday Inn Express New York - Manhattan West Side by IHG</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
@@ -77794,7 +77794,7 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -77826,7 +77826,7 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>(512307) - Holiday Inn Orlando International Dr-ICON by IHG</t>
+          <t>Holiday Inn Orlando International Dr-ICON by IHG</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -77836,7 +77836,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -77868,7 +77868,7 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>(219851) - Holiday Inn Bristol City Centre by IHG</t>
+          <t>Holiday Inn Bristol City Centre by IHG</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
@@ -77878,7 +77878,7 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -77910,7 +77910,7 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>(228567) - Kimpton Charlotte Square by IHG</t>
+          <t>Kimpton Charlotte Square by IHG</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
@@ -77920,7 +77920,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -77952,7 +77952,7 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>(129903) - RIHGA Royal Hotel Osaka, Vignette Collection by IHG</t>
+          <t>RIHGA Royal Hotel Osaka, Vignette Collection by IHG</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
@@ -77962,7 +77962,7 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
@@ -77994,7 +77994,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>(100328) - Imperial Las Perlas</t>
+          <t>Imperial Las Perlas</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -78004,7 +78004,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -78036,7 +78036,7 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>(210653) - Royalton Riviera Cancun, An Autograph Collection All-Inclusive Resort &amp; Casino</t>
+          <t>Royalton Riviera Cancun, An Autograph Collection All-Inclusive Resort &amp; Casino</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -78046,7 +78046,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -78078,7 +78078,7 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>(129766) - Holiday Inn Osaka Namba by IHG</t>
+          <t>Holiday Inn Osaka Namba by IHG</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -78088,7 +78088,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -78120,7 +78120,7 @@
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>(506020) - Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Bronx - Zoo Area by IHG</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -78130,7 +78130,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -78162,7 +78162,7 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>(136246) - Holiday Inn Tbilisi by IHG</t>
+          <t>Holiday Inn Tbilisi by IHG</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -78172,7 +78172,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -78204,7 +78204,7 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>(165366) - Crowne Plaza College Park - Washington DC by IHG</t>
+          <t>Crowne Plaza College Park - Washington DC by IHG</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
@@ -78214,7 +78214,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -78246,7 +78246,7 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>(546925) - Crowne Plaza PHU QUOC STARBAY by IHG</t>
+          <t>Crowne Plaza PHU QUOC STARBAY by IHG</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
@@ -78256,7 +78256,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
@@ -78288,7 +78288,7 @@
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>(481409) - Holiday Inn Express MUNICH - CITY EAST by IHG</t>
+          <t>Holiday Inn Express MUNICH - CITY EAST by IHG</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
@@ -78298,7 +78298,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
@@ -78330,7 +78330,7 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>(123825) - Hotel Indigo Glasgow by IHG</t>
+          <t>Hotel Indigo Glasgow by IHG</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
@@ -78340,7 +78340,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -78372,7 +78372,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>(493382) - Holiday Inn &amp; Suites Jakarta Gajah Mada by IHG</t>
+          <t>Holiday Inn &amp; Suites Jakarta Gajah Mada by IHG</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -78382,7 +78382,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -78414,7 +78414,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>(283467) - Holiday Inn Express London - ExCeL by IHG</t>
+          <t>Holiday Inn Express London - ExCeL by IHG</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -78424,7 +78424,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -78456,7 +78456,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>(105159) - Crowne Plaza Newark Airport by IHG</t>
+          <t>Crowne Plaza Newark Airport by IHG</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -78466,7 +78466,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -78498,7 +78498,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>(211757) - Crowne Plaza Melbourne by IHG</t>
+          <t>Crowne Plaza Melbourne by IHG</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -78508,7 +78508,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -78540,7 +78540,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>(111965) - Crowne Plaza Frankfurt Congress Hotel by IHG</t>
+          <t>Crowne Plaza Frankfurt Congress Hotel by IHG</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -78550,7 +78550,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -78582,7 +78582,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>(121035) - InterContinental Marseille - Hotel Dieu by IHG</t>
+          <t>InterContinental Marseille - Hotel Dieu by IHG</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -78592,7 +78592,7 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -78624,7 +78624,7 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>(492790) - Holiday Inn Express Liverpool Central by IHG</t>
+          <t>Holiday Inn Express Liverpool Central by IHG</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
@@ -78634,7 +78634,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
@@ -78666,7 +78666,7 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>(239652) - Holiday Inn Express &amp; Suites Miami Airport East by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Miami Airport East by IHG</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -78676,7 +78676,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -78708,7 +78708,7 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>(228651) - InterContinental Edinburgh The George by IHG</t>
+          <t>InterContinental Edinburgh The George by IHG</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -78718,7 +78718,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -78750,7 +78750,7 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>(117463) - Grand Hyatt Denver</t>
+          <t>Grand Hyatt Denver</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -78760,7 +78760,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -78792,7 +78792,7 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>(107757) - Kimpton Theta New York - Times Square by IHG</t>
+          <t>Kimpton Theta New York - Times Square by IHG</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -78802,7 +78802,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -78834,7 +78834,7 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>(167152) - Holiday Inn Express &amp; Suites Asheville Downtown by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Asheville Downtown by IHG</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
@@ -78844,7 +78844,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -78876,7 +78876,7 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>(143708) - InterContinental Hanoi Westlake by IHG</t>
+          <t>InterContinental Hanoi Westlake by IHG</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
@@ -78886,7 +78886,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -78918,7 +78918,7 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>(360241) - Holiday Inn Express &amp; Suites Downtown Ottawa East by IHG</t>
+          <t>Holiday Inn Express &amp; Suites Downtown Ottawa East by IHG</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
@@ -78928,7 +78928,7 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -78960,7 +78960,7 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>(108804) - Kimpton Hotel Eventi by IHG</t>
+          <t>Kimpton Hotel Eventi by IHG</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
@@ -78970,7 +78970,7 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -79002,7 +79002,7 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>(101372) - Mahekal Beach Front Resort &amp; Spa</t>
+          <t>Mahekal Beach Front Resort &amp; Spa</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
@@ -79012,7 +79012,7 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -79044,7 +79044,7 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>(547726) - Holiday Inn Express Düsseldorf – Hauptbahnhof by IHG</t>
+          <t>Holiday Inn Express Düsseldorf – Hauptbahnhof by IHG</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
@@ -79054,7 +79054,7 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -79086,7 +79086,7 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>(231691) - SAHARA Las Vegas</t>
+          <t>SAHARA Las Vegas</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
@@ -79096,7 +79096,7 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>SynXis</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -79128,7 +79128,7 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>(143373) - Crowne Plaza Danang City Centre by IHG</t>
+          <t>Crowne Plaza Danang City Centre by IHG</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
@@ -79138,7 +79138,7 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -79170,7 +79170,7 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>(311431) - Hyatt Regency Cartagena</t>
+          <t>Hyatt Regency Cartagena</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
@@ -79180,7 +79180,7 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -79212,7 +79212,7 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>(101629) - Secrets Maroma Beach Riviera Cancun - Solo Adultos</t>
+          <t>Secrets Maroma Beach Riviera Cancun - Solo Adultos</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
@@ -79222,7 +79222,7 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -79254,7 +79254,7 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>(126531) - Hyatt Regency Huntington Beach Resort and Spa</t>
+          <t>Hyatt Regency Huntington Beach Resort and Spa</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
@@ -79264,7 +79264,7 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -79296,7 +79296,7 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>(550407) - Hotel Indigo PANAMA CITY MARINA by IHG</t>
+          <t>Hotel Indigo PANAMA CITY MARINA by IHG</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
@@ -79306,7 +79306,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -79338,7 +79338,7 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>(120074) - Crowne Plaza Paris Republique by IHG</t>
+          <t>Crowne Plaza Paris Republique by IHG</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
@@ -79348,7 +79348,7 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -79380,7 +79380,7 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>(208877) - Holiday Inn Panama Distrito Financiero by IHG</t>
+          <t>Holiday Inn Panama Distrito Financiero by IHG</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
@@ -79390,7 +79390,7 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -79422,7 +79422,7 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>(100078) - Posada Real Puerto Escondido</t>
+          <t>Posada Real Puerto Escondido</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
@@ -79432,7 +79432,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -79464,7 +79464,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>(547780) - Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
+          <t>Holiday Inn - the niu, MESH STUTTGART MESSE by IHG</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -79474,7 +79474,7 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -79506,7 +79506,7 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>(111284) - Hyatt Regency Denver Tech Center</t>
+          <t>Hyatt Regency Denver Tech Center</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
@@ -79516,7 +79516,7 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -79548,7 +79548,7 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>(114325) - Crowne Plaza London - Kings Cross by IHG</t>
+          <t>Crowne Plaza London - Kings Cross by IHG</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
@@ -79558,7 +79558,7 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -79590,7 +79590,7 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>(127435) - InterContinental Istanbul by IHG</t>
+          <t>InterContinental Istanbul by IHG</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
@@ -79600,7 +79600,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -79632,7 +79632,7 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>(143321) - InterContinental Danang Sun Peninsula Resort by IHG</t>
+          <t>InterContinental Danang Sun Peninsula Resort by IHG</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
@@ -79642,7 +79642,7 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -79674,7 +79674,7 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>(107809) - Holiday Inn Washington-Central/White House by IHG</t>
+          <t>Holiday Inn Washington-Central/White House by IHG</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
@@ -79684,7 +79684,7 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>DerbySoft</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12359,7 +12359,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12698,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15605,7 +15605,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15758,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -15911,7 +15911,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19505,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -23804,7 +23804,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28103,7 +28103,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -29761,7 +29761,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33355,7 +33355,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -33774,7 +33774,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38067,7 +38067,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38227,7 +38227,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42825,7 +42825,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -42985,7 +42985,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45069,7 +45069,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -49368,7 +49368,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -51441,7 +51441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52979,7 +52979,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56573,7 +56573,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -56992,7 +56992,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -61291,7 +61291,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -65589,7 +65589,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -69583,7 +69583,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71441,7 +71441,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75035,7 +75035,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -75454,7 +75454,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 25/05/2026 23:40 · W20 · 12-18 may 2026</t>
+          <t>Generado: 25/05/2026 23:53 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 00:29 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:08 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 01:25 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:28 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:34 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:45 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 02:52 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-21/Analisis_Checkrates_7d.xlsx
+++ b/checkrates/week-21/Analisis_Checkrates_7d.xlsx
@@ -569,7 +569,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -8297,7 +8297,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -13114,7 +13114,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16021,7 +16021,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16327,7 +16327,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16487,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -19921,7 +19921,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -28519,7 +28519,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30178,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34277,7 +34277,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -34696,7 +34696,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -38989,7 +38989,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -39149,7 +39149,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43747,7 +43747,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -43907,7 +43907,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -45991,7 +45991,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -50290,7 +50290,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -52363,7 +52363,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -53902,7 +53902,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58001,7 +58001,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58420,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -62719,7 +62719,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -67017,7 +67017,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -71011,7 +71011,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -72870,7 +72870,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -76845,7 +76845,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
@@ -77264,7 +77264,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 26/05/2026 03:05 · W20 · 12-18 may 2026</t>
+          <t>Generado: 26/05/2026 03:15 · W20 · 12-18 may 2026</t>
         </is>
       </c>
     </row>
